--- a/00_Проект/02_Реестр/Реестр_терминов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_терминов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр терминов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр терминов'!$A$1:$D$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр терминов'!$A$1:$D$30</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
   <si>
     <t xml:space="preserve">Термин</t>
   </si>
@@ -101,6 +101,222 @@
   </si>
   <si>
     <t xml:space="preserve">19–21, 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент теплопередачи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Величина, характеризующая интенсивность передачи тепла от одного теплоносителя к другому через разделяющую стенку; снижается при образовании отложений на поверхности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия, 01_Стандарты_СТД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КПД котла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отношение тепловой энергии, фактически переданной воде, к энергии, выделившейся при сжигании топлива</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-002, ЭНЦ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД, 04_Энциклопедия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неполнота сгорания топлива</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отклонение от оптимального соотношения топливо/воздух в горелке, снижающее КПД и увеличивающее сажеобразование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-002, 10_Каталог_неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия, 10_Каталог_неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кавитация</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Образование и схлопывание пузырьков пара в зоне пониженного давления на входе в рабочее колесо насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-003, 10_Каталог_неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Напор насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перепад давления, создаваемый насосом за счёт передачи механической энергии рабочего колеса потоку жидкости</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-003, ЭНЦ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дисбаланс ротора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неравномерное распределение массы вращающегося ротора, вызывающее вибрацию, синхронную с частотой вращения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сопротивление изоляции обмотки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электрическая характеристика обмотки электродвигателя, снижение которой указывает на риск повреждения изоляции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наряд-допуск</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Документ, разрешающий выполнение работ повышенной опасности с указанием условий безопасного производства работ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Регламенты_РГЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тепловая энергия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Энергетический ресурс, при потреблении которого изменяются термодинамические параметры теплоносителя (температура, давление)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФЗ №190-ФЗ «О теплоснабжении», ст. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16_Нормативные_документы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теплоноситель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пар или вода, используемые для передачи тепловой энергии; в контексте систем отопления и вентиляции — рабочая среда этих систем</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФЗ №190-ФЗ, ст. 2; ГОСТ 22270-2018, п. 2.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16_Нормативные_документы, 01_Стандарты_СТД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Источник тепловой энергии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Устройство, предназначенное для производства тепловой энергии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФЗ №190-ФЗ, ст. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тепловая сеть</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Совокупность устройств (включая тепловые пункты, насосные станции), предназначенных для передачи тепловой энергии и теплоносителя от источников тепловой энергии до теплопотребляющих установок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Система теплоснабжения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Совокупность источников тепловой энергии и теплопотребляющих установок, технологически соединённых тепловыми сетями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Надёжность теплоснабжения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Характеристика состояния системы теплоснабжения, при котором обеспечиваются качество и безопасность теплоснабжения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коммерческий учёт тепловой энергии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Установление количества и качества производимой, передаваемой или потребляемой тепловой энергии и теплоносителя с помощью приборов учёта либо расчётным путём</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теплообменник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Устройство, в котором осуществляется бесконтактный процесс теплообмена между жидкими и/или газообразными средами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГОСТ 22270-2018, п. 2.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16_Нормативные_документы, 01_Стандарты_СТД, 04_Энциклопедия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Водяное отопление</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вид отопления помещений с помощью жидкого теплоносителя (воды или другой жидкости)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГОСТ 22270-2018, п. 2.70.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бак-аккумулятор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резервуар для накопления и хранения нагретого или охлаждённого теплоносителя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГОСТ 22270-2018, п. 2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тепловой пункт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сооружение с комплектом оборудования, позволяющее изменить температурный и гидравлический режимы теплоносителя, обеспечить учёт и регулирование расхода тепловой энергии и теплоносителя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СП 124.13330.2012, п. 3.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16_Нормативные_документы, 01_Стандарты_СТД, 02_Регламенты_РГЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Индивидуальный тепловой пункт (ИТП)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тепловой пункт, предназначенный для присоединения систем отопления, вентиляции, горячего водоснабжения одного здания или его части</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СП 124.13330.2012, п. 3.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Центральный тепловой пункт (ЦТП)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тепловой пункт, предназначенный для присоединения систем двух и более зданий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СП 124.13330.2012, п. 3.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автоматизированный узел управления (АУУ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Устройство с комплектом оборудования, устанавливаемое в месте подключения системы отопления здания к распределительным тепловым сетям от ЦТП, позволяющее изменить температурный и гидравлический режимы и обеспечить учёт расхода тепловой энергии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СП 124.13330.2012, п. 3.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Система централизованного теплоснабжения (СЦТ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Система, состоящая из одного или нескольких источников теплоты, тепловых сетей и потребителей теплоты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СП 124.13330.2012, п. 3.1</t>
   </si>
 </sst>
 </file>
@@ -211,8 +427,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -505,115 +725,437 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D30"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_терминов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_терминов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр терминов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр терминов'!$A$1:$D$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр терминов'!$A$1:$D$34</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="110">
   <si>
     <t xml:space="preserve">Термин</t>
   </si>
@@ -317,6 +317,42 @@
   </si>
   <si>
     <t xml:space="preserve">СП 124.13330.2012, п. 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТЭН (трубчатый электронагреватель)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нагревательный элемент, преобразующий электрическую энергию в тепловую за счёт прохождения тока через спираль внутри металлической трубки, изолированную прессованным диэлектриком</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД, 02_Регламенты_РГЛ, 04_Энциклопедия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Колосниковая решётка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Элемент топки твердотопливного котла, на котором размещается слой топлива и через который проходит воздух для горения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тяга</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разрежение в топке и дымоходе, создаваемое разницей плотностей горячих дымовых газов и наружного воздуха (либо принудительно), обеспечивающее подачу воздуха для горения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зашлаковывание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Спекание золы в плотную корку на колосниковой решётке, перекрывающее проходные отверстия для воздуха</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-005, 10_Каталог_неисправностей</t>
   </si>
 </sst>
 </file>
@@ -432,15 +468,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -725,7 +761,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -1154,8 +1190,64 @@
         <v>56</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D30"/>
+  <autoFilter ref="A1:D34"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
